--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,28 +100,28 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C20427</t>
+    <t>GEN-092.04.12</t>
+  </si>
+  <si>
+    <t>Autre gestion des effets secondaires</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>372559001</t>
   </si>
   <si>
     <t>facteur de croissance hématopoïétique</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>GEN-092.04.12</t>
-  </si>
-  <si>
-    <t>Autre gestion des effets secondaires</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>

--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-gestion-effet-secondaire-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260716085853</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-07-16T08:58:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
